--- a/evidence/s03a/race/s02a_shipments.xlsx
+++ b/evidence/s03a/race/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>d0ce2297778afa882c6c7e9a231c25e3</t>
+    <t>0e0ae38748a961d8cb2553c11054594d</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>561ed99c1c85b9bf18c80a16292ae347</t>
+    <t>6b5f5a2aec6eaf17fd130db6487a98be</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:00:52+08:00</t>
+    <t>2026-10-27T00:27:04+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/race/s02a_shipments.xlsx
+++ b/evidence/s03a/race/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>0e0ae38748a961d8cb2553c11054594d</t>
+    <t>194d6461cf6bc2c38d66d08309ff2756</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>6b5f5a2aec6eaf17fd130db6487a98be</t>
+    <t>ac8ef525184246c042e0c1dbb2e2db74</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:27:04+08:00</t>
+    <t>2026-10-27T00:32:46+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/race/s02a_shipments.xlsx
+++ b/evidence/s03a/race/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>194d6461cf6bc2c38d66d08309ff2756</t>
+    <t>1bfd53e65a5491ae0229c4545a7e81ba</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>ac8ef525184246c042e0c1dbb2e2db74</t>
+    <t>3d764b5c4632a27f79d22a7a21231505</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:32:46+08:00</t>
+    <t>2026-10-27T00:40:42+08:00</t>
   </si>
   <si>
     <t>precision</t>
